--- a/order_management/24.12-booth-release-and-inventory-behaviour/24.12 - Booth Release and Other Products Inventory Behaviour.xlsx
+++ b/order_management/24.12-booth-release-and-inventory-behaviour/24.12 - Booth Release and Other Products Inventory Behaviour.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cross-Epic Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Implementation Status" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$7</definedName>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -142,6 +143,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -646,6 +651,54 @@
       </c>
       <c r="B13" s="8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not started — analysis only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impl Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impl Commits</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -659,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -673,6 +726,7 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,6 +785,11 @@
           <t>Confluence</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Impl Status (2026-07-01)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -784,6 +843,11 @@
           <t>Open §Order Management → Story 24.12</t>
         </is>
       </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -837,6 +901,11 @@
           <t>Open §Order Management → Story 24.12</t>
         </is>
       </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -890,6 +959,11 @@
           <t>Open §Order Management → Story 24.12</t>
         </is>
       </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -943,6 +1017,11 @@
           <t>Open §Order Management → Story 24.12</t>
         </is>
       </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started (Blocked — Social Tables / floorplan automatic booth-release API integration (external, not built))</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -996,6 +1075,11 @@
           <t>Open §Order Management → Story 24.12</t>
         </is>
       </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1047,6 +1131,11 @@
       <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.12</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -1145,11 +1234,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1163,6 +1254,16 @@
           <t>Open Question</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Resolution / Decision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -1171,6 +1272,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Should the manual-release reminder be gated by a configurable 'floorplan auto-release supported' signal (e.g. derived from Show.floor_plan_link presence or a new flag) so it disappears once a Social Tables release integration ships, or simply shown for every canceled order containing booth lines? No auto-release support signal exists in code today, so the only buildable behaviour now is to always show it; whether to add a future-proofing flag is a product decision not derivable from code.</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>OPEN — for team discussion</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Current direction (2026-07-01): lean toward always showing the reminder for every canceled order containing booth lines (only behaviour buildable today — no auto-release signal exists); add a future-proofing flag only if/when a Social Tables release integration is scoped — pending team confirmation.</t>
         </is>
       </c>
     </row>
@@ -1230,4 +1341,190 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Not started — analysis/feasibility stage only; no branch or SBE ticket cut yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>— (not started). No SBE ticket / PR / Swagger tag yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>24.12-a</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started — net-new admin cancel endpoint (transition order to canceled).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>24.12-b</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started — release booth reservations (committed→released) on cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>24.12-c</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started — release non-booth product reservations on cancel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>24.12-d</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started (Blocked — Social Tables / floorplan automatic booth-release API integration, external, not built).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>24.12-e</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started — manual-release reminder note surfaced in cancel popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>24.12-f</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>◻ Not started — backend-enforced release inside the cancel $transaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Remaining — all</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Everything is unbuilt: 24.12-a, 24.12-b, 24.12-c, 24.12-d (Blocked), 24.12-e, 24.12-f.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Open decision — reminder gating</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Show the manual-release reminder always, or gate it behind a configurable 'floorplan auto-release supported' signal so it disappears once a Social Tables release integration ships? Current direction: always show (only buildable behaviour today) — pending team confirmation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Dependency — Social Tables</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>24.12-d depends on an external Social Tables / floorplan automatic booth-release API integration (not built or scoped; only a stored display URL Show.floor_plan_link exists).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Dependency — story 24.10</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>The cancel action (POST /api/v1/orders/:id/cancel) is owned by story 24.10; 24.12 owns only the inventory-release side-effect on that same endpoint (no separate route).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Out of API scope</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Front-end wiring (cancel popup rendering of the reminder) is outside API scope.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>